--- a/quizzes/peinture-17e-niveau2.xlsx
+++ b/quizzes/peinture-17e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6FB997-0A13-463E-951B-A7D8484F59D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A07116-0D51-49BE-AC65-09766ED3A473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,9 +112,6 @@
     <t>Paysage avec la fuite en Égypte</t>
   </si>
   <si>
-    <t>Anthony van Dyck</t>
-  </si>
-  <si>
     <t>1635</t>
   </si>
   <si>
@@ -196,9 +193,6 @@
     <t>Autoportrait</t>
   </si>
   <si>
-    <t>Charles Le Brun</t>
-  </si>
-  <si>
     <t>1655-1661</t>
   </si>
   <si>
@@ -217,9 +211,6 @@
     <t>Le Débarquement de Cléopâtre à Tarse</t>
   </si>
   <si>
-    <t>David Teniers le Jeune</t>
-  </si>
-  <si>
     <t>1642</t>
   </si>
   <si>
@@ -247,9 +238,6 @@
     <t>La Chasse de Diane</t>
   </si>
   <si>
-    <t>Eustache Le Sueur</t>
-  </si>
-  <si>
     <t>1652-1655</t>
   </si>
   <si>
@@ -565,9 +553,6 @@
     <t>La Présentation au Temple</t>
   </si>
   <si>
-    <t>Willem Claesz. Heda</t>
-  </si>
-  <si>
     <t>Nature morte avec coupe dorée</t>
   </si>
   <si>
@@ -577,9 +562,6 @@
     <t>Nature morte avec cor à boire du corps de Saint-Sébastien</t>
   </si>
   <si>
-    <t>Willem van de Velde le Jeune</t>
-  </si>
-  <si>
     <t>Le Canon de salut</t>
   </si>
   <si>
@@ -607,9 +589,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/9/92/Annibale_Carracci_003.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/ae/Portrait_de_Charles_1er%2C_roi_d%27Angleterre%2C_%C3%A0_la_chasse_-_Antoon_van_Dyck_-_Mus%C3%A9e_du_Louvre_Peintures_INV_1236_%3B_MR_666.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/GENTILESCHI_Judith.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -619,9 +598,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/6/61/Murillo_immaculate_conception.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/50/Bernardo_Strozzi_-_The_Cook_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/1/1e/Bacchus_%28by_Michelangelo_Merisi_da_Caravaggio%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -631,15 +607,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Charles_Le_Brun_-_Pierre_S%C3%A9guier%2C_chancelier_de_France_%281655-1661%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/0a/David_Teniers_%28II%29_-_Smoker_Leaning_his_Elbow_on_a_Table_-_WGA22080.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b1/Las_Meninas%2C_by_Diego_Vel%C3%A1zquez%2C_from_Prado_in_Google_EarthFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/e/e6/Domenichino_-_La_caccia_di_Diana_%28Galleria_Borghese%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -655,9 +625,6 @@
     <t>Musée du Palais National, Taipei</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/97/Cavalier_soldier_Hals-1624x.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f6/Frans_Snyders_-_Fish_Stall_-_WGA21521FXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -667,9 +634,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/f/fe/Woman_Reading_a_Letter_by_Gabri%C3%ABl_Metsu.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/91/La_Tour_Le_Tricheur_Louvre_RF1972-8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/9f/Gerard_Dou_-_The_Dropsical_Woman_-_WGA06647.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -682,27 +646,18 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/a/a3/Guido_Reni_-_Aurora_-_WGA19273.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/af/Avercamp%2C_Hendrick_-_Winterlandschap_met_schaatsers_-_SK-A-1718.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/81/Hishikawa_Moronobu_-_Beauty_Looking_Back_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/8d/Autoportrait_au_turban_%28Perpignan%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8f/Jordaens_King_Drinks_1638-40.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/7/74/Jacob_Isaacksz._van_Ruisdael_-_Le_Moulin_de_Wijk-bij-Duurstede.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/0c/Jan_Lievens_Portrait_of_Rembrandt.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/01/Goyen_1651_View_of_Dordrecht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Musée de Dordrecht</t>
   </si>
   <si>
@@ -712,9 +667,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/Jos%C3%A9_de_Ribera_-_Clubfooted_Boy_-_WGA19376.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Arbre de bambou et prune dans la neige</t>
   </si>
   <si>
@@ -733,27 +685,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/1/17/Mattia_preti%2C_convito_di_assalonne%2C_1660-65_ca.%2C_Q254.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/62/Meindert_Hobbema_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/c/c2/The_idle_servant.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/12/Judith_et_sa_servante%2C_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/1e/Hampton_Court_Palace_Duchess_of_Cumberland_Peter_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Barbara Villiers, duchesse de Cleveland (Les Beautés de Windsor)</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/82/Le_v%C5%93u_de_Louis_XIII.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -766,9 +703,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/c/c2/Pieter_de_Hooch_-_The_Courtyard_of_a_House_in_Delft.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Ceiling_of_Palazzo_Barberini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/The_Nightwatch_by_Rembrandt_-_Rijksmuseum.jpg/3840px-The_Nightwatch_by_Rembrandt_-_Rijksmuseum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -784,12 +718,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/9/91/Simon_Vouet_-_Presentation_in_the_Temple_-_WGA25366.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/e8/Still_Life_with_Gilt_Goblet_1635_Willem_Claesz_Heda.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/e/ed/Het_Kanonschot_-_Canon_fired_%28Willem_van_de_Velde_II%2C_1707%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -805,16 +733,88 @@
     <t>La Fille malade</t>
   </si>
   <si>
-    <t>Caravaggio ou Caravage</t>
-  </si>
-  <si>
-    <t>Annibale Carracci ou Carrache</t>
-  </si>
-  <si>
-    <t>Guercino ou Guerchin</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Van_Dyck_Charles_I_1635.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/87/Bernardo_Strozzi_-_The_Cook_-_WGA21913.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/69/Analyasis_of_Las_Meninas.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Frans_Hals_%E2%80%93_The_Laughing_Cavalier.jpg/960px-Frans_Hals_%E2%80%93_The_Laughing_Cavalier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1f/Hendrick_Avercamp_-_Winterlandschap_met_ijsvermaak.jpg/1280px-Hendrick_Avercamp_-_Winterlandschap_met_ijsvermaak.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/bc/Jacob_Jordaens_-_The_Bean_King_%28Louvre%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Goyen_1651_View_of_Dordrecht.jpg/1280px-Goyen_1651_View_of_Dordrecht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/Meindert_Hobbema_001.jpg/1280px-Meindert_Hobbema_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Judith_et_sa_servante%2C_par_Orazio_Gentileschi.jpg/960px-Judith_et_sa_servante%2C_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6e/Ceiling_of_Palazzo_Barberini.jpg/960px-Ceiling_of_Palazzo_Barberini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/26/Stilleven_met_vergulde_bokaal_Rijksmuseum_SK-A-4830.jpeg/1280px-Stilleven_met_vergulde_bokaal_Rijksmuseum_SK-A-4830.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Antoine van DYCK</t>
+  </si>
+  <si>
+    <t>Annibale CARRACI ou CARRACHE</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO ou CARAVAGE</t>
+  </si>
+  <si>
+    <t>Charles LE BRUN</t>
+  </si>
+  <si>
+    <t>David TENIERS LE JEUNE</t>
+  </si>
+  <si>
+    <t>Eustache LE SUEUR</t>
+  </si>
+  <si>
+    <t>Willem van de VELDE LE JEUNE</t>
+  </si>
+  <si>
+    <t>Willem CLAESZOON HEDA</t>
+  </si>
+  <si>
+    <t>GUERCINO ou GUERCHIN</t>
   </si>
 </sst>
 </file>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>18</v>
@@ -1289,15 +1289,15 @@
         <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>23</v>
@@ -1306,7 +1306,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>26</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>27</v>
@@ -1331,180 +1331,180 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>199</v>
+        <v>239</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>58</v>
+        <v>259</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C15" s="4">
         <v>1635</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="C17" s="4">
         <v>1643</v>
@@ -1513,134 +1513,134 @@
         <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>8</v>
@@ -1649,15 +1649,15 @@
         <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>15</v>
@@ -1666,236 +1666,236 @@
         <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="13.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C37" s="4">
         <v>1651</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>11</v>
@@ -1904,100 +1904,100 @@
         <v>20</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:5" s="8" customFormat="1">
       <c r="A41" s="5" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C41" s="7">
         <v>1634</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C43" s="4">
         <v>1663</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>21</v>
@@ -2006,168 +2006,168 @@
         <v>22</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C56" s="4">
         <v>1649</v>
@@ -2176,41 +2176,41 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2218,16 +2218,16 @@
         <v>254</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2235,7 +2235,7 @@
         <v>255</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>13</v>
@@ -2244,24 +2244,24 @@
         <v>22</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>185</v>
+        <v>262</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2271,60 +2271,60 @@
     <hyperlink ref="A4" r:id="rId3" xr:uid="{0A6A3DED-DD12-4780-B3AE-753A687E8FBB}"/>
     <hyperlink ref="A5" r:id="rId4" xr:uid="{1B59958E-18C4-44A5-910B-4A37D44E0416}"/>
     <hyperlink ref="A6" r:id="rId5" xr:uid="{BF908DEB-302B-4A7D-9647-D1EFA4FA35C0}"/>
-    <hyperlink ref="A7" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/a/ae/Portrait_de_Charles_1er%2C_roi_d%27Angleterre%2C_%C3%A0_la_chasse_-_Antoon_van_Dyck_-_Mus%C3%A9e_du_Louvre_Peintures_INV_1236_%3B_MR_666.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original" xr:uid="{B1DA1517-CFBD-43D9-993F-6C9F657DECB4}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
-    <hyperlink ref="A9" r:id="rId8" xr:uid="{443377B4-B04D-403D-A824-DB13768731AF}"/>
-    <hyperlink ref="A10" r:id="rId9" xr:uid="{96AEEB4F-086F-426E-B93A-2DA57DE54BFE}"/>
-    <hyperlink ref="A11" r:id="rId10" xr:uid="{2C71B471-4CE8-429D-B25A-38AAD873211F}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{8D66B7E5-4F81-473E-BAC6-3A133A8BF0A1}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{410B345F-73DD-447C-9423-97EB3B76E6DA}"/>
-    <hyperlink ref="A14" r:id="rId13" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
-    <hyperlink ref="A16" r:id="rId14" display="https://upload.wikimedia.org/wikipedia/commons/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{EF1DEDB6-C815-4BDA-9879-3384057FFBDB}"/>
-    <hyperlink ref="A17" r:id="rId15" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
-    <hyperlink ref="A18" r:id="rId16" xr:uid="{E295B8A2-C5BB-45D7-9AA7-E002F85E21B1}"/>
-    <hyperlink ref="A19" r:id="rId17" xr:uid="{05771483-93F6-4474-B4B2-32295BDD81BC}"/>
-    <hyperlink ref="A20" r:id="rId18" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
-    <hyperlink ref="A21" r:id="rId19" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
-    <hyperlink ref="A15" r:id="rId20" xr:uid="{410386BC-CF6D-4493-8184-0403996A2394}"/>
-    <hyperlink ref="A22" r:id="rId21" xr:uid="{5B67177B-3566-448C-82E8-B3E47FC7E769}"/>
-    <hyperlink ref="A23" r:id="rId22" xr:uid="{08DD652B-0E47-4AEF-AE3B-843EED3B5D37}"/>
-    <hyperlink ref="A24" r:id="rId23" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
-    <hyperlink ref="A25" r:id="rId24" xr:uid="{8D4F9315-2578-4A82-A162-B6F8D1439BCA}"/>
-    <hyperlink ref="A26" r:id="rId25" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
-    <hyperlink ref="A27" r:id="rId26" xr:uid="{74A7EC9A-D21C-4ECC-949D-FCC02E532D40}"/>
-    <hyperlink ref="A28" r:id="rId27" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
-    <hyperlink ref="A29" r:id="rId28" xr:uid="{7E575697-1670-41B2-BC75-9872FD034F04}"/>
-    <hyperlink ref="A30" r:id="rId29" xr:uid="{C56A21A7-BA62-4ADB-A8E1-875A3978D465}"/>
-    <hyperlink ref="A31" r:id="rId30" xr:uid="{E9D4827D-694A-41D2-9587-D78CF34633D6}"/>
-    <hyperlink ref="A32" r:id="rId31" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
-    <hyperlink ref="A33" r:id="rId32" xr:uid="{39A0F762-D90E-4572-9DEC-9EA918318ACF}"/>
-    <hyperlink ref="A34" r:id="rId33" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
-    <hyperlink ref="A35" r:id="rId34" xr:uid="{F55798B2-2CE8-4A25-815E-90D86322A818}"/>
-    <hyperlink ref="A37" r:id="rId35" xr:uid="{360DE5AA-3E6B-4B70-92A1-E33A17D256DC}"/>
-    <hyperlink ref="A38" r:id="rId36" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
-    <hyperlink ref="A39" r:id="rId37" xr:uid="{3BE0486C-7F43-481A-86BD-951F21E28A4C}"/>
-    <hyperlink ref="A42" r:id="rId38" xr:uid="{C2924DD1-C68C-444A-A0E3-59C8E373AD89}"/>
-    <hyperlink ref="A43" r:id="rId39" xr:uid="{75B759AD-4F67-448E-B557-AEA72EFC75A5}"/>
-    <hyperlink ref="A44" r:id="rId40" xr:uid="{CD9775EB-2654-4C75-971C-D0D4D92F6FFA}"/>
-    <hyperlink ref="A45" r:id="rId41" xr:uid="{2BF6D38A-2C06-4EB1-83D9-ADA687CE29F2}"/>
-    <hyperlink ref="A46" r:id="rId42" xr:uid="{5EB8FE73-1B38-4EE8-9F5D-408471533360}"/>
-    <hyperlink ref="A47" r:id="rId43" xr:uid="{8AB4CB1D-C2C6-41EA-890E-ABACF970DD91}"/>
-    <hyperlink ref="A48" r:id="rId44" xr:uid="{FB460A1A-07EA-48A8-9D24-E0EB432A0123}"/>
-    <hyperlink ref="A49" r:id="rId45" xr:uid="{5BB0097B-55F4-42A3-92F7-B32B91E9112E}"/>
-    <hyperlink ref="A50" r:id="rId46" xr:uid="{01EA9FE3-3B2A-42AC-A1F3-B75B9ACC1DFF}"/>
-    <hyperlink ref="A51" r:id="rId47" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
-    <hyperlink ref="A52" r:id="rId48" xr:uid="{148877A9-A1F7-456C-A81C-37672CB63775}"/>
-    <hyperlink ref="A53" r:id="rId49" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
-    <hyperlink ref="A54" r:id="rId50" xr:uid="{E70300CA-0777-4952-90C0-98EF3B6AD5F8}"/>
-    <hyperlink ref="A55" r:id="rId51" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
-    <hyperlink ref="A56" r:id="rId52" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
-    <hyperlink ref="A57" r:id="rId53" xr:uid="{2C4AA8F5-D564-4836-B8DB-CC33D50B9F4C}"/>
-    <hyperlink ref="A58" r:id="rId54" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
-    <hyperlink ref="A59" r:id="rId55" xr:uid="{272E99F1-3024-4F10-BE75-D7BBEDD80ACD}"/>
-    <hyperlink ref="A60" r:id="rId56" xr:uid="{869EEE74-EC55-442B-878C-AA7159427BE6}"/>
-    <hyperlink ref="A40" r:id="rId57" xr:uid="{8B20EDCD-1325-45F5-8F5D-A7C167C88195}"/>
-    <hyperlink ref="A36" r:id="rId58" xr:uid="{4E0A47A0-C017-478F-882E-CB36E0739B68}"/>
-    <hyperlink ref="A41" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5AF78C13-26E9-461E-B73A-B7874AC748C6}"/>
+    <hyperlink ref="A8" r:id="rId6" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
+    <hyperlink ref="A9" r:id="rId7" xr:uid="{443377B4-B04D-403D-A824-DB13768731AF}"/>
+    <hyperlink ref="A10" r:id="rId8" xr:uid="{96AEEB4F-086F-426E-B93A-2DA57DE54BFE}"/>
+    <hyperlink ref="A12" r:id="rId9" xr:uid="{8D66B7E5-4F81-473E-BAC6-3A133A8BF0A1}"/>
+    <hyperlink ref="A14" r:id="rId10" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
+    <hyperlink ref="A17" r:id="rId11" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
+    <hyperlink ref="A19" r:id="rId12" xr:uid="{05771483-93F6-4474-B4B2-32295BDD81BC}"/>
+    <hyperlink ref="A20" r:id="rId13" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
+    <hyperlink ref="A21" r:id="rId14" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
+    <hyperlink ref="A15" r:id="rId15" xr:uid="{410386BC-CF6D-4493-8184-0403996A2394}"/>
+    <hyperlink ref="A23" r:id="rId16" xr:uid="{08DD652B-0E47-4AEF-AE3B-843EED3B5D37}"/>
+    <hyperlink ref="A24" r:id="rId17" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
+    <hyperlink ref="A26" r:id="rId18" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
+    <hyperlink ref="A27" r:id="rId19" xr:uid="{74A7EC9A-D21C-4ECC-949D-FCC02E532D40}"/>
+    <hyperlink ref="A28" r:id="rId20" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
+    <hyperlink ref="A29" r:id="rId21" xr:uid="{7E575697-1670-41B2-BC75-9872FD034F04}"/>
+    <hyperlink ref="A31" r:id="rId22" xr:uid="{E9D4827D-694A-41D2-9587-D78CF34633D6}"/>
+    <hyperlink ref="A32" r:id="rId23" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
+    <hyperlink ref="A34" r:id="rId24" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
+    <hyperlink ref="A35" r:id="rId25" xr:uid="{F55798B2-2CE8-4A25-815E-90D86322A818}"/>
+    <hyperlink ref="A38" r:id="rId26" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
+    <hyperlink ref="A39" r:id="rId27" xr:uid="{3BE0486C-7F43-481A-86BD-951F21E28A4C}"/>
+    <hyperlink ref="A42" r:id="rId28" xr:uid="{C2924DD1-C68C-444A-A0E3-59C8E373AD89}"/>
+    <hyperlink ref="A43" r:id="rId29" xr:uid="{75B759AD-4F67-448E-B557-AEA72EFC75A5}"/>
+    <hyperlink ref="A44" r:id="rId30" xr:uid="{CD9775EB-2654-4C75-971C-D0D4D92F6FFA}"/>
+    <hyperlink ref="A46" r:id="rId31" xr:uid="{5EB8FE73-1B38-4EE8-9F5D-408471533360}"/>
+    <hyperlink ref="A51" r:id="rId32" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
+    <hyperlink ref="A52" r:id="rId33" xr:uid="{148877A9-A1F7-456C-A81C-37672CB63775}"/>
+    <hyperlink ref="A53" r:id="rId34" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
+    <hyperlink ref="A55" r:id="rId35" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
+    <hyperlink ref="A56" r:id="rId36" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
+    <hyperlink ref="A57" r:id="rId37" xr:uid="{2C4AA8F5-D564-4836-B8DB-CC33D50B9F4C}"/>
+    <hyperlink ref="A58" r:id="rId38" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
+    <hyperlink ref="A36" r:id="rId39" xr:uid="{4E0A47A0-C017-478F-882E-CB36E0739B68}"/>
+    <hyperlink ref="A41" r:id="rId40" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5AF78C13-26E9-461E-B73A-B7874AC748C6}"/>
+    <hyperlink ref="A7" r:id="rId41" xr:uid="{8F4B7051-A843-4632-824C-A44F2EFF1A24}"/>
+    <hyperlink ref="A11" r:id="rId42" xr:uid="{AB2FF381-1824-400A-9BCD-9866E6CB0543}"/>
+    <hyperlink ref="A13" r:id="rId43" xr:uid="{DCC4F749-42F9-4EA6-B692-38BDBFED8233}"/>
+    <hyperlink ref="A16" r:id="rId44" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D4203C8E-14B3-4039-BB62-7E3865A15809}"/>
+    <hyperlink ref="A18" r:id="rId45" xr:uid="{4E85BF3A-C7F1-4E5B-9573-8D70D234C5FE}"/>
+    <hyperlink ref="A22" r:id="rId46" xr:uid="{5CD46D31-5953-4A01-A434-5588D8535138}"/>
+    <hyperlink ref="A25" r:id="rId47" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CEC1CD09-7664-45E7-A13A-1C89874F9D17}"/>
+    <hyperlink ref="A30" r:id="rId48" xr:uid="{0F121F29-C0EE-4A69-9EFA-A138C1AB816A}"/>
+    <hyperlink ref="A33" r:id="rId49" xr:uid="{462E3B14-36A0-4360-9820-4A3EBD2EFC5E}"/>
+    <hyperlink ref="A37" r:id="rId50" xr:uid="{D9F18DF3-6619-40EF-97D9-920D7EDAF9C0}"/>
+    <hyperlink ref="A40" r:id="rId51" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96CB3FBB-D488-4EA8-947C-196A5F59B5CC}"/>
+    <hyperlink ref="A45" r:id="rId52" xr:uid="{2DED679E-C744-4A9B-BE0E-3AC4E0186B76}"/>
+    <hyperlink ref="A47" r:id="rId53" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E3A7419A-96A2-4726-8D79-92D233EEF839}"/>
+    <hyperlink ref="A48" r:id="rId54" xr:uid="{3DA6F16C-EF9E-4846-A7D5-E3E407DD7B4C}"/>
+    <hyperlink ref="A49" r:id="rId55" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{35574EF1-90A2-4482-A075-ABF3F82885AB}"/>
+    <hyperlink ref="A50" r:id="rId56" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{6BB625E2-11FD-4585-B272-667B24656B6E}"/>
+    <hyperlink ref="A54" r:id="rId57" xr:uid="{83398DF1-6CCA-4D96-A783-0FE96B2E9F31}"/>
+    <hyperlink ref="A59" r:id="rId58" xr:uid="{83B8C51F-09BE-47B7-B07C-3A8576A86413}"/>
+    <hyperlink ref="A60" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{66426EEF-8035-4F74-A518-75CD002F4D21}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-17e-niveau2.xlsx
+++ b/quizzes/peinture-17e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A07116-0D51-49BE-AC65-09766ED3A473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F487C44-2844-44B4-9717-33EE5E8FC477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="265">
   <si>
     <t>image</t>
   </si>
@@ -169,12 +169,6 @@
     <t>Palazzo Barberini, Rome</t>
   </si>
   <si>
-    <t>1596-1597</t>
-  </si>
-  <si>
-    <t>Bacchus</t>
-  </si>
-  <si>
     <t>Galleria Nazionale d'Arte Antica, Rome</t>
   </si>
   <si>
@@ -598,9 +592,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/6/61/Murillo_immaculate_conception.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/1e/Bacchus_%28by_Michelangelo_Merisi_da_Caravaggio%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/5b/Carel_Fabritius_-_The_Goldfinch_-_605_-_Mauritshuis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -815,6 +806,15 @@
   </si>
   <si>
     <t>GUERCINO ou GUERCHIN</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/48/The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg/1280px-The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>Eglise Saint-Louis-des-Français, Rome</t>
+  </si>
+  <si>
+    <t>La Vocation de saint Matthieu</t>
   </si>
 </sst>
 </file>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>18</v>
@@ -1289,15 +1289,15 @@
         <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>23</v>
@@ -1306,7 +1306,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>26</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>27</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>30</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>32</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>38</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>42</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>45</v>
@@ -1416,95 +1416,95 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>255</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1600</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>263</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C15" s="4">
         <v>1635</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C17" s="4">
         <v>1643</v>
@@ -1513,134 +1513,134 @@
         <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>8</v>
@@ -1649,15 +1649,15 @@
         <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>15</v>
@@ -1666,236 +1666,236 @@
         <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="13.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C37" s="4">
         <v>1651</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>11</v>
@@ -1904,100 +1904,100 @@
         <v>20</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:5" s="8" customFormat="1">
       <c r="A41" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C41" s="7">
         <v>1634</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C43" s="4">
         <v>1663</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>21</v>
@@ -2006,38 +2006,38 @@
         <v>22</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>37</v>
@@ -2045,129 +2045,129 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="E49" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C56" s="4">
         <v>1649</v>
@@ -2176,49 +2176,49 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>30</v>
@@ -2227,15 +2227,15 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>13</v>
@@ -2244,24 +2244,24 @@
         <v>22</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2274,57 +2274,56 @@
     <hyperlink ref="A8" r:id="rId6" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
     <hyperlink ref="A9" r:id="rId7" xr:uid="{443377B4-B04D-403D-A824-DB13768731AF}"/>
     <hyperlink ref="A10" r:id="rId8" xr:uid="{96AEEB4F-086F-426E-B93A-2DA57DE54BFE}"/>
-    <hyperlink ref="A12" r:id="rId9" xr:uid="{8D66B7E5-4F81-473E-BAC6-3A133A8BF0A1}"/>
-    <hyperlink ref="A14" r:id="rId10" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
-    <hyperlink ref="A17" r:id="rId11" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
-    <hyperlink ref="A19" r:id="rId12" xr:uid="{05771483-93F6-4474-B4B2-32295BDD81BC}"/>
-    <hyperlink ref="A20" r:id="rId13" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
-    <hyperlink ref="A21" r:id="rId14" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
-    <hyperlink ref="A15" r:id="rId15" xr:uid="{410386BC-CF6D-4493-8184-0403996A2394}"/>
-    <hyperlink ref="A23" r:id="rId16" xr:uid="{08DD652B-0E47-4AEF-AE3B-843EED3B5D37}"/>
-    <hyperlink ref="A24" r:id="rId17" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
-    <hyperlink ref="A26" r:id="rId18" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
-    <hyperlink ref="A27" r:id="rId19" xr:uid="{74A7EC9A-D21C-4ECC-949D-FCC02E532D40}"/>
-    <hyperlink ref="A28" r:id="rId20" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
-    <hyperlink ref="A29" r:id="rId21" xr:uid="{7E575697-1670-41B2-BC75-9872FD034F04}"/>
-    <hyperlink ref="A31" r:id="rId22" xr:uid="{E9D4827D-694A-41D2-9587-D78CF34633D6}"/>
-    <hyperlink ref="A32" r:id="rId23" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
-    <hyperlink ref="A34" r:id="rId24" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
-    <hyperlink ref="A35" r:id="rId25" xr:uid="{F55798B2-2CE8-4A25-815E-90D86322A818}"/>
-    <hyperlink ref="A38" r:id="rId26" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
-    <hyperlink ref="A39" r:id="rId27" xr:uid="{3BE0486C-7F43-481A-86BD-951F21E28A4C}"/>
-    <hyperlink ref="A42" r:id="rId28" xr:uid="{C2924DD1-C68C-444A-A0E3-59C8E373AD89}"/>
-    <hyperlink ref="A43" r:id="rId29" xr:uid="{75B759AD-4F67-448E-B557-AEA72EFC75A5}"/>
-    <hyperlink ref="A44" r:id="rId30" xr:uid="{CD9775EB-2654-4C75-971C-D0D4D92F6FFA}"/>
-    <hyperlink ref="A46" r:id="rId31" xr:uid="{5EB8FE73-1B38-4EE8-9F5D-408471533360}"/>
-    <hyperlink ref="A51" r:id="rId32" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
-    <hyperlink ref="A52" r:id="rId33" xr:uid="{148877A9-A1F7-456C-A81C-37672CB63775}"/>
-    <hyperlink ref="A53" r:id="rId34" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
-    <hyperlink ref="A55" r:id="rId35" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
-    <hyperlink ref="A56" r:id="rId36" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
-    <hyperlink ref="A57" r:id="rId37" xr:uid="{2C4AA8F5-D564-4836-B8DB-CC33D50B9F4C}"/>
-    <hyperlink ref="A58" r:id="rId38" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
-    <hyperlink ref="A36" r:id="rId39" xr:uid="{4E0A47A0-C017-478F-882E-CB36E0739B68}"/>
-    <hyperlink ref="A41" r:id="rId40" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5AF78C13-26E9-461E-B73A-B7874AC748C6}"/>
-    <hyperlink ref="A7" r:id="rId41" xr:uid="{8F4B7051-A843-4632-824C-A44F2EFF1A24}"/>
-    <hyperlink ref="A11" r:id="rId42" xr:uid="{AB2FF381-1824-400A-9BCD-9866E6CB0543}"/>
-    <hyperlink ref="A13" r:id="rId43" xr:uid="{DCC4F749-42F9-4EA6-B692-38BDBFED8233}"/>
-    <hyperlink ref="A16" r:id="rId44" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D4203C8E-14B3-4039-BB62-7E3865A15809}"/>
-    <hyperlink ref="A18" r:id="rId45" xr:uid="{4E85BF3A-C7F1-4E5B-9573-8D70D234C5FE}"/>
-    <hyperlink ref="A22" r:id="rId46" xr:uid="{5CD46D31-5953-4A01-A434-5588D8535138}"/>
-    <hyperlink ref="A25" r:id="rId47" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CEC1CD09-7664-45E7-A13A-1C89874F9D17}"/>
-    <hyperlink ref="A30" r:id="rId48" xr:uid="{0F121F29-C0EE-4A69-9EFA-A138C1AB816A}"/>
-    <hyperlink ref="A33" r:id="rId49" xr:uid="{462E3B14-36A0-4360-9820-4A3EBD2EFC5E}"/>
-    <hyperlink ref="A37" r:id="rId50" xr:uid="{D9F18DF3-6619-40EF-97D9-920D7EDAF9C0}"/>
-    <hyperlink ref="A40" r:id="rId51" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96CB3FBB-D488-4EA8-947C-196A5F59B5CC}"/>
-    <hyperlink ref="A45" r:id="rId52" xr:uid="{2DED679E-C744-4A9B-BE0E-3AC4E0186B76}"/>
-    <hyperlink ref="A47" r:id="rId53" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E3A7419A-96A2-4726-8D79-92D233EEF839}"/>
-    <hyperlink ref="A48" r:id="rId54" xr:uid="{3DA6F16C-EF9E-4846-A7D5-E3E407DD7B4C}"/>
-    <hyperlink ref="A49" r:id="rId55" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{35574EF1-90A2-4482-A075-ABF3F82885AB}"/>
-    <hyperlink ref="A50" r:id="rId56" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{6BB625E2-11FD-4585-B272-667B24656B6E}"/>
-    <hyperlink ref="A54" r:id="rId57" xr:uid="{83398DF1-6CCA-4D96-A783-0FE96B2E9F31}"/>
-    <hyperlink ref="A59" r:id="rId58" xr:uid="{83B8C51F-09BE-47B7-B07C-3A8576A86413}"/>
-    <hyperlink ref="A60" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{66426EEF-8035-4F74-A518-75CD002F4D21}"/>
+    <hyperlink ref="A14" r:id="rId9" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
+    <hyperlink ref="A17" r:id="rId10" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
+    <hyperlink ref="A19" r:id="rId11" xr:uid="{05771483-93F6-4474-B4B2-32295BDD81BC}"/>
+    <hyperlink ref="A20" r:id="rId12" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
+    <hyperlink ref="A21" r:id="rId13" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{410386BC-CF6D-4493-8184-0403996A2394}"/>
+    <hyperlink ref="A23" r:id="rId15" xr:uid="{08DD652B-0E47-4AEF-AE3B-843EED3B5D37}"/>
+    <hyperlink ref="A24" r:id="rId16" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
+    <hyperlink ref="A26" r:id="rId17" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
+    <hyperlink ref="A27" r:id="rId18" xr:uid="{74A7EC9A-D21C-4ECC-949D-FCC02E532D40}"/>
+    <hyperlink ref="A28" r:id="rId19" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
+    <hyperlink ref="A29" r:id="rId20" xr:uid="{7E575697-1670-41B2-BC75-9872FD034F04}"/>
+    <hyperlink ref="A31" r:id="rId21" xr:uid="{E9D4827D-694A-41D2-9587-D78CF34633D6}"/>
+    <hyperlink ref="A32" r:id="rId22" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
+    <hyperlink ref="A34" r:id="rId23" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
+    <hyperlink ref="A35" r:id="rId24" xr:uid="{F55798B2-2CE8-4A25-815E-90D86322A818}"/>
+    <hyperlink ref="A38" r:id="rId25" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
+    <hyperlink ref="A39" r:id="rId26" xr:uid="{3BE0486C-7F43-481A-86BD-951F21E28A4C}"/>
+    <hyperlink ref="A42" r:id="rId27" xr:uid="{C2924DD1-C68C-444A-A0E3-59C8E373AD89}"/>
+    <hyperlink ref="A43" r:id="rId28" xr:uid="{75B759AD-4F67-448E-B557-AEA72EFC75A5}"/>
+    <hyperlink ref="A44" r:id="rId29" xr:uid="{CD9775EB-2654-4C75-971C-D0D4D92F6FFA}"/>
+    <hyperlink ref="A46" r:id="rId30" xr:uid="{5EB8FE73-1B38-4EE8-9F5D-408471533360}"/>
+    <hyperlink ref="A51" r:id="rId31" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
+    <hyperlink ref="A52" r:id="rId32" xr:uid="{148877A9-A1F7-456C-A81C-37672CB63775}"/>
+    <hyperlink ref="A53" r:id="rId33" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
+    <hyperlink ref="A55" r:id="rId34" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
+    <hyperlink ref="A56" r:id="rId35" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
+    <hyperlink ref="A57" r:id="rId36" xr:uid="{2C4AA8F5-D564-4836-B8DB-CC33D50B9F4C}"/>
+    <hyperlink ref="A58" r:id="rId37" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
+    <hyperlink ref="A36" r:id="rId38" xr:uid="{4E0A47A0-C017-478F-882E-CB36E0739B68}"/>
+    <hyperlink ref="A41" r:id="rId39" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5AF78C13-26E9-461E-B73A-B7874AC748C6}"/>
+    <hyperlink ref="A7" r:id="rId40" xr:uid="{8F4B7051-A843-4632-824C-A44F2EFF1A24}"/>
+    <hyperlink ref="A11" r:id="rId41" xr:uid="{AB2FF381-1824-400A-9BCD-9866E6CB0543}"/>
+    <hyperlink ref="A13" r:id="rId42" xr:uid="{DCC4F749-42F9-4EA6-B692-38BDBFED8233}"/>
+    <hyperlink ref="A16" r:id="rId43" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D4203C8E-14B3-4039-BB62-7E3865A15809}"/>
+    <hyperlink ref="A18" r:id="rId44" xr:uid="{4E85BF3A-C7F1-4E5B-9573-8D70D234C5FE}"/>
+    <hyperlink ref="A22" r:id="rId45" xr:uid="{5CD46D31-5953-4A01-A434-5588D8535138}"/>
+    <hyperlink ref="A25" r:id="rId46" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CEC1CD09-7664-45E7-A13A-1C89874F9D17}"/>
+    <hyperlink ref="A30" r:id="rId47" xr:uid="{0F121F29-C0EE-4A69-9EFA-A138C1AB816A}"/>
+    <hyperlink ref="A33" r:id="rId48" xr:uid="{462E3B14-36A0-4360-9820-4A3EBD2EFC5E}"/>
+    <hyperlink ref="A37" r:id="rId49" xr:uid="{D9F18DF3-6619-40EF-97D9-920D7EDAF9C0}"/>
+    <hyperlink ref="A40" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96CB3FBB-D488-4EA8-947C-196A5F59B5CC}"/>
+    <hyperlink ref="A45" r:id="rId51" xr:uid="{2DED679E-C744-4A9B-BE0E-3AC4E0186B76}"/>
+    <hyperlink ref="A47" r:id="rId52" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E3A7419A-96A2-4726-8D79-92D233EEF839}"/>
+    <hyperlink ref="A48" r:id="rId53" xr:uid="{3DA6F16C-EF9E-4846-A7D5-E3E407DD7B4C}"/>
+    <hyperlink ref="A49" r:id="rId54" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{35574EF1-90A2-4482-A075-ABF3F82885AB}"/>
+    <hyperlink ref="A50" r:id="rId55" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{6BB625E2-11FD-4585-B272-667B24656B6E}"/>
+    <hyperlink ref="A54" r:id="rId56" xr:uid="{83398DF1-6CCA-4D96-A783-0FE96B2E9F31}"/>
+    <hyperlink ref="A59" r:id="rId57" xr:uid="{83B8C51F-09BE-47B7-B07C-3A8576A86413}"/>
+    <hyperlink ref="A60" r:id="rId58" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{66426EEF-8035-4F74-A518-75CD002F4D21}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-17e-niveau2.xlsx
+++ b/quizzes/peinture-17e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F487C44-2844-44B4-9717-33EE5E8FC477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCA447DE-56A8-485A-8EE8-938D912FC114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="237">
   <si>
     <t>image</t>
   </si>
@@ -37,79 +37,31 @@
     <t>titre de l'œuvre</t>
   </si>
   <si>
-    <t>Adriaen Brouwer</t>
-  </si>
-  <si>
     <t>Gemäldegalerie, Dresde</t>
   </si>
   <si>
-    <t>1636</t>
-  </si>
-  <si>
-    <t>1636-1638</t>
-  </si>
-  <si>
-    <t>Städel Museum, Francfort</t>
-  </si>
-  <si>
-    <t>Le Goûteur amer</t>
-  </si>
-  <si>
-    <t>1630</t>
-  </si>
-  <si>
-    <t>Adriaen van Ostade</t>
-  </si>
-  <si>
-    <t>1653</t>
+    <t>Alte Pinakothek, Munich</t>
   </si>
   <si>
     <t>Musée du Louvre, Paris</t>
   </si>
   <si>
-    <t>1663</t>
-  </si>
-  <si>
-    <t>Le Peintre dans son atelier</t>
-  </si>
-  <si>
     <t>Rijksmuseum, Amsterdam</t>
   </si>
   <si>
-    <t>Aelbert Cuyp</t>
-  </si>
-  <si>
     <t>1650</t>
   </si>
   <si>
-    <t>National Gallery of Art, Washington</t>
-  </si>
-  <si>
-    <t>1655</t>
-  </si>
-  <si>
     <t>National Gallery, Londres</t>
   </si>
   <si>
-    <t>Alonso Cano</t>
-  </si>
-  <si>
     <t>Museo del Prado, Madrid</t>
   </si>
   <si>
-    <t>1646-1652</t>
-  </si>
-  <si>
-    <t>Christ mort soutenu par un ange</t>
-  </si>
-  <si>
-    <t>1604</t>
-  </si>
-  <si>
-    <t>Galleria Doria Pamphilj, Rome</t>
-  </si>
-  <si>
-    <t>Paysage avec la fuite en Égypte</t>
+    <t>1602</t>
+  </si>
+  <si>
+    <t>Le Christ apparaissant à saint Pierre (Domine, quo vadis?)</t>
   </si>
   <si>
     <t>1635</t>
@@ -118,6 +70,15 @@
     <t>Charles Ier à la chasse</t>
   </si>
   <si>
+    <t>1637-1638</t>
+  </si>
+  <si>
+    <t>Portrait équestre de Charles Ier</t>
+  </si>
+  <si>
+    <t>1637</t>
+  </si>
+  <si>
     <t>Artemisia Gentileschi</t>
   </si>
   <si>
@@ -130,31 +91,25 @@
     <t>Judith décapitant Holopherne</t>
   </si>
   <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>Schloss Weissenstein, Pommersfelden</t>
+  </si>
+  <si>
+    <t>Suzanne et les vieillards</t>
+  </si>
+  <si>
     <t>1625</t>
   </si>
   <si>
-    <t>Judith et sa servante</t>
-  </si>
-  <si>
-    <t>Bada Shanren</t>
-  </si>
-  <si>
-    <t>XVIIe siècle</t>
-  </si>
-  <si>
-    <t>Cleveland Museum of Art, Cleveland</t>
-  </si>
-  <si>
-    <t>Poissons et rochers</t>
-  </si>
-  <si>
     <t>Bartolomé Esteban Murillo</t>
   </si>
   <si>
-    <t>1678</t>
-  </si>
-  <si>
-    <t>L'Immaculée Conception des Vénérables</t>
+    <t>1645-1646</t>
+  </si>
+  <si>
+    <t>Les Enfants mangeant des raisins et un melon</t>
   </si>
   <si>
     <t>Bernardo Strozzi</t>
@@ -166,10 +121,10 @@
     <t>La Cuisinière</t>
   </si>
   <si>
-    <t>Palazzo Barberini, Rome</t>
-  </si>
-  <si>
-    <t>Galleria Nazionale d'Arte Antica, Rome</t>
+    <t>Église Saint-Louis-des-Français, Rome</t>
+  </si>
+  <si>
+    <t>La Vocation de saint Matthieu</t>
   </si>
   <si>
     <t>Carel Fabritius</t>
@@ -184,18 +139,21 @@
     <t>Le Chardonneret</t>
   </si>
   <si>
+    <t>Vue de Delft</t>
+  </si>
+  <si>
     <t>Autoportrait</t>
   </si>
   <si>
+    <t>1660-1661</t>
+  </si>
+  <si>
     <t>1655-1661</t>
   </si>
   <si>
     <t>Portrait du chancelier Séguier</t>
   </si>
   <si>
-    <t>Chen Hongshou</t>
-  </si>
-  <si>
     <t>Claude Lorrain</t>
   </si>
   <si>
@@ -205,12 +163,21 @@
     <t>Le Débarquement de Cléopâtre à Tarse</t>
   </si>
   <si>
+    <t>1648</t>
+  </si>
+  <si>
+    <t>Paysage avec l'embarquement de la reine de Saba</t>
+  </si>
+  <si>
     <t>1642</t>
   </si>
   <si>
     <t>Le Fumeur</t>
   </si>
   <si>
+    <t>1651</t>
+  </si>
+  <si>
     <t>Diego Velázquez</t>
   </si>
   <si>
@@ -220,31 +187,28 @@
     <t>Les Ménines</t>
   </si>
   <si>
-    <t>Domenichino</t>
-  </si>
-  <si>
-    <t>1616-1617</t>
+    <t>1634-1635</t>
+  </si>
+  <si>
+    <t>La Reddition de Breda (Les Lances)</t>
   </si>
   <si>
     <t>Galleria Borghese, Rome</t>
   </si>
   <si>
-    <t>La Chasse de Diane</t>
-  </si>
-  <si>
-    <t>1652-1655</t>
-  </si>
-  <si>
-    <t>Melpomène, Érato et Polymnie</t>
+    <t>1649</t>
+  </si>
+  <si>
+    <t>La Prédication de saint Paul à Éphèse</t>
+  </si>
+  <si>
+    <t>1645-1648</t>
   </si>
   <si>
     <t>Francisco de Zurbarán</t>
   </si>
   <si>
-    <t>1635-1640</t>
-  </si>
-  <si>
-    <t>L'Agneau de Dieu (Agnus Dei)</t>
+    <t>Nature morte avec des vases</t>
   </si>
   <si>
     <t>Frans Hals</t>
@@ -268,57 +232,66 @@
     <t>Gabriel Metsu</t>
   </si>
   <si>
-    <t>1664-1666</t>
-  </si>
-  <si>
-    <t>National Gallery of Ireland, Dublin</t>
-  </si>
-  <si>
-    <t>Femme lisant une lettre</t>
+    <t>1661-1662</t>
+  </si>
+  <si>
+    <t>Le Marché aux légumes à Amsterdam</t>
   </si>
   <si>
     <t>Georges de La Tour</t>
   </si>
   <si>
-    <t>Le Tricheur à l'as de carreau</t>
-  </si>
-  <si>
     <t>1640-1645</t>
   </si>
   <si>
+    <t>La Madeleine à la veilleuse</t>
+  </si>
+  <si>
+    <t>Musée des Beaux-Arts, Rennes</t>
+  </si>
+  <si>
+    <t>Le Nouveau-né</t>
+  </si>
+  <si>
     <t>Gerard Dou</t>
   </si>
   <si>
-    <t>La Femme hydropique</t>
-  </si>
-  <si>
     <t>1658</t>
   </si>
   <si>
     <t>1665</t>
   </si>
   <si>
+    <t>J. Paul Getty Museum, Los Angeles</t>
+  </si>
+  <si>
+    <t>L'Astronome à la lumière d'une bougie</t>
+  </si>
+  <si>
     <t>Gerrit van Honthorst</t>
   </si>
   <si>
-    <t>1617</t>
-  </si>
-  <si>
-    <t>Le Christ devant le grand prêtre</t>
-  </si>
-  <si>
-    <t>Galleria degli Uffizi, Florence</t>
-  </si>
-  <si>
-    <t>1618-1622</t>
-  </si>
-  <si>
-    <t>Et in Arcadia ego (Les Bergers d'Arcadie)</t>
+    <t>Centraal Museum, Utrecht</t>
+  </si>
+  <si>
+    <t>L'Entremetteuse</t>
+  </si>
+  <si>
+    <t>1623</t>
+  </si>
+  <si>
+    <t>1621</t>
   </si>
   <si>
     <t>Casino dell'Aurora, Rome</t>
   </si>
   <si>
+    <t>L'Aurore (plafond de la Villa Ludovisi)</t>
+  </si>
+  <si>
+    <t>1631</t>
+  </si>
+  <si>
     <t>Guido Reni</t>
   </si>
   <si>
@@ -328,9 +301,6 @@
     <t>L'Aurore (plafond du Casino Rospigliosi)</t>
   </si>
   <si>
-    <t>Museo di Capodimonte, Naples</t>
-  </si>
-  <si>
     <t>Hendrick Avercamp</t>
   </si>
   <si>
@@ -343,18 +313,6 @@
     <t>Fitzwilliam Museum, Cambridge</t>
   </si>
   <si>
-    <t>Hishikawa Moronobu</t>
-  </si>
-  <si>
-    <t>1682-1683</t>
-  </si>
-  <si>
-    <t>Musée national de Tokyo, Tokyo</t>
-  </si>
-  <si>
-    <t>Beauté regardant en arrière (Mihaeri Bijin-zu)</t>
-  </si>
-  <si>
     <t>Hyacinthe Rigaud</t>
   </si>
   <si>
@@ -367,18 +325,12 @@
     <t>Autoportrait au turban</t>
   </si>
   <si>
-    <t>1689</t>
-  </si>
-  <si>
     <t>Jacob Jordaens</t>
   </si>
   <si>
     <t>Le Roi boit !</t>
   </si>
   <si>
-    <t>1638</t>
-  </si>
-  <si>
     <t>Jacob van Ruisdael</t>
   </si>
   <si>
@@ -391,13 +343,13 @@
     <t>Musée de l'Ermitage, Saint-Pétersbourg</t>
   </si>
   <si>
-    <t>Jan Lievens</t>
-  </si>
-  <si>
-    <t>1629</t>
-  </si>
-  <si>
-    <t>Portrait du jeune Rembrandt</t>
+    <t>Jan Steen</t>
+  </si>
+  <si>
+    <t>1665-1668</t>
+  </si>
+  <si>
+    <t>La Fête de Saint-Nicolas</t>
   </si>
   <si>
     <t>Jan van Goyen</t>
@@ -415,19 +367,25 @@
     <t>La Jeune Fille à la perle</t>
   </si>
   <si>
+    <t>1658-1661</t>
+  </si>
+  <si>
+    <t>La Laitière</t>
+  </si>
+  <si>
     <t>José de Ribera</t>
   </si>
   <si>
     <t>Le Pied-bot</t>
   </si>
   <si>
+    <t>1632</t>
+  </si>
+  <si>
     <t>Judith Leyster</t>
   </si>
   <si>
-    <t>Kanō Tan'yū</t>
-  </si>
-  <si>
-    <t>Château de Nagoya, Nagoya</t>
+    <t>La Proposition galante</t>
   </si>
   <si>
     <t>Louis Le Nain</t>
@@ -436,28 +394,22 @@
     <t>Le Repas de paysans</t>
   </si>
   <si>
+    <t>La Forge</t>
+  </si>
+  <si>
     <t>Luca Giordano</t>
   </si>
   <si>
-    <t>Mattia Preti</t>
-  </si>
-  <si>
-    <t>1655-1660</t>
-  </si>
-  <si>
-    <t>Le Banquet d'Absalon</t>
+    <t>Le Jugement de Salomon</t>
+  </si>
+  <si>
+    <t>1680</t>
   </si>
   <si>
     <t>Meindert Hobbema</t>
   </si>
   <si>
-    <t>L'Avenue à Middelharnis</t>
-  </si>
-  <si>
-    <t>Nicolaes Maes</t>
-  </si>
-  <si>
-    <t>La Servante paresseuse</t>
+    <t>Le Moulin à eau</t>
   </si>
   <si>
     <t>Nicolas Poussin</t>
@@ -469,21 +421,6 @@
     <t>Les Bergers d'Arcadie</t>
   </si>
   <si>
-    <t>Orazio Gentileschi</t>
-  </si>
-  <si>
-    <t>1608-1609</t>
-  </si>
-  <si>
-    <t>Peter Lely</t>
-  </si>
-  <si>
-    <t>1660-1665</t>
-  </si>
-  <si>
-    <t>Hampton Court Palace, Londres</t>
-  </si>
-  <si>
     <t>Peter Paul Rubens</t>
   </si>
   <si>
@@ -496,19 +433,22 @@
     <t>La Descente de croix</t>
   </si>
   <si>
+    <t>1610-1611</t>
+  </si>
+  <si>
+    <t>L'Érection de la croix</t>
+  </si>
+  <si>
     <t>Philippe de Champaigne</t>
   </si>
   <si>
-    <t>Musée des Beaux-Arts, Caen</t>
-  </si>
-  <si>
-    <t>Le Voeu de Louis XIII</t>
+    <t>Portrait triple du cardinal de Richelieu</t>
   </si>
   <si>
     <t>Pieter Claesz</t>
   </si>
   <si>
-    <t>Nature morte au hareng</t>
+    <t>Nature morte aux instruments de musique</t>
   </si>
   <si>
     <t>Pieter de Hooch</t>
@@ -517,24 +457,21 @@
     <t>La Cour d'une maison à Delft</t>
   </si>
   <si>
-    <t>Pietro da Cortona</t>
-  </si>
-  <si>
-    <t>1633-1639</t>
-  </si>
-  <si>
-    <t>Le Triomphe de la Divine Providence (plafond)</t>
-  </si>
-  <si>
     <t>Rembrandt van Rijn</t>
   </si>
   <si>
     <t>La Ronde de nuit</t>
   </si>
   <si>
+    <t>La Leçon d'anatomie du docteur Tulp</t>
+  </si>
+  <si>
     <t>Salomon van Ruysdael</t>
   </si>
   <si>
+    <t>Paysage fluvial avec voiliers</t>
+  </si>
+  <si>
     <t>Salvator Rosa</t>
   </si>
   <si>
@@ -547,49 +484,22 @@
     <t>La Présentation au Temple</t>
   </si>
   <si>
-    <t>Nature morte avec coupe dorée</t>
-  </si>
-  <si>
-    <t>Willem Kalf</t>
-  </si>
-  <si>
-    <t>Nature morte avec cor à boire du corps de Saint-Sébastien</t>
-  </si>
-  <si>
-    <t>Le Canon de salut</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/87/Adriaen_Brouwer_-_The_Bitter_Potion_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/df/Adriaen_van_Ostade_006.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/c/c9/Cattle_in_a_River_-_Albert_Cuyp.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Bovins dans la rivière</t>
-  </si>
-  <si>
-    <t>Musée des Beaux-Arts, Budapest</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/26/Alonso_Cano_-_The_Dead_Christ_Supported_by_an_Angel_-_WGA3993.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Dans plus de langues</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/92/Annibale_Carracci_003.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/16/Annibale_Carracci_-_Domine_quo_vadis%3F_-_WGA04444.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/98/Anthonis_van_Dyck_-_Equestrian_Portrait_of_Charles_I_-_National_Gallery%2C_London.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/GENTILESCHI_Judith.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/0d/Bada_Shanren_%28Chinese%2C_1626-1705%29_-_Fish_and_Rocks_-_1953.247_-_Cleveland_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/61/Murillo_immaculate_conception.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/0/04/Susanna_and_the_Elders_%281610%29%2C_Artemisia_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/7b/Bartolom%C3%A9_Esteban_Perez_Murillo_-_Grape_and_Melon_Eaters.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/77/0_%27La_Vocation_de_saint_Matthieu%27_de_Le_Caravage_-_fr2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/5b/Carel_Fabritius_-_The_Goldfinch_-_605_-_Mauritshuis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
@@ -601,19 +511,10 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/0/0a/David_Teniers_%28II%29_-_Smoker_Leaning_his_Elbow_on_a_Table_-_WGA22080.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/e6/Domenichino_-_La_caccia_di_Diana_%28Galleria_Borghese%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Le_Sueur%2C_Eustache_-_Melpom%C3%A8ne%2C_%C3%89rato_et_Polymnie_-_1652_-_1655.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/ef/Francisco_de_Zurbar%C3%A1n_006.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/75/Chen_hongshou_selfportrait%2C1635_-_crop.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Musée du Palais National, Taipei</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/a3/Eustache_Le_Sueur_-_The_Preaching_of_St_Paul_at_Ephesus_-_WGA12613.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/0/0c/Bodeg%C3%B3n_de_recipientes_%28Zurbar%C3%A1n%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f6/Frans_Snyders_-_Fish_Stall_-_WGA21521FXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
@@ -622,31 +523,25 @@
     <t>1625-1650</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/f/fe/Woman_Reading_a_Letter_by_Gabri%C3%ABl_Metsu.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/9f/Gerard_Dou_-_The_Dropsical_Woman_-_WGA06647.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8d/Gerard_van_Honthorst_-_Christ_before_the_High_Priest_-_WGA11650.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b9/Et-in-Arcadia-ego.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/63/Le_March%C3%A9_aux_herbes_d%27Amsterdam_-_Gabriel_Metsu_-_Mus%C3%A9e_du_Louvre_Peintures_INV_1460.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/c/ce/Gerard_van_Honthorst_-_The_procuress_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/85/Guercino_-_Ceiling_painting%2C_Casino_dell%27Aurora%2C_11aurora.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/a/a3/Guido_Reni_-_Aurora_-_WGA19273.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/81/Hishikawa_Moronobu_-_Beauty_Looking_Back_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/8d/Autoportrait_au_turban_%28Perpignan%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/7/74/Jacob_Isaacksz._van_Ruisdael_-_Le_Moulin_de_Wijk-bij-Duurstede.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/0c/Jan_Lievens_Portrait_of_Rembrandt.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/86/Jan_Havicksz._Steen_%E2%80%93_Het_Sint-Nicolaasfeest_%E2%80%93_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
     <t>Musée de Dordrecht</t>
@@ -655,40 +550,34 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0f/1665_Girl_with_a_Pearl_Earring.jpg/1920px-1665_Girl_with_a_Pearl_Earring.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/5a/Johannes_Vermeer_-_De_melkmeid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/Jos%C3%A9_de_Ribera_-_Clubfooted_Boy_-_WGA19376.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Arbre de bambou et prune dans la neige</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c7/Le_Nain_-_Repas_de_paysans_%281642%29.jpg/1280px-Le_Nain_-_Repas_de_paysans_%281642%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/ab/Luca_Giordano_-_Marriage_at_Cana.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>Museo nazionale di Capodimonte</t>
-  </si>
-  <si>
-    <t>Les Noces de Cana</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/17/Mattia_preti%2C_convito_di_assalonne%2C_1660-65_ca.%2C_Q254.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/c/c2/The_idle_servant.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Barbara Villiers, duchesse de Cleveland (Les Beautés de Windsor)</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/82/Le_v%C5%93u_de_Louis_XIII.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/9/93/Pieter_Claesz_-_Herring_with_bread_and_beer_-_1122_%28OK%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Musée Boijmans Van Beuningen, Rotterdam</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a5/%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg/1920px-%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d2/Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg/1280px-Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Palais des Médicis Riccardi, Florence</t>
+  </si>
+  <si>
+    <t>L’apothéose des Médicis</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d9/Nicolas_Poussin_078.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/77/Kardinaal_de_Richelieu.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Claesz.%2C_Pieter_-_Still_Life_with_Musical_Instruments_-_1623.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/c/c2/Pieter_de_Hooch_-_The_Courtyard_of_a_House_in_Delft.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
@@ -697,10 +586,7 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/The_Nightwatch_by_Rembrandt_-_Rijksmuseum.jpg/3840px-The_Nightwatch_by_Rembrandt_-_Rijksmuseum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Paysage fluvial avec ferry </t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/78/Rivierlandschap_met_een_veerboot_Rijksmuseum_SK-C-1698.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/13/Salomon_van_Ruysdael_-_View_of_Sailing_Boats_on_a_Lake_-_1044_-_Mauritshuis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/1/12/Salvator_Rosa_-_Human_Fragility_-_WGA20047.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
@@ -709,22 +595,22 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/9/91/Simon_Vouet_-_Presentation_in_the_Temple_-_WGA25366.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/ed/Het_Kanonschot_-_Canon_fired_%28Willem_van_de_Velde_II%2C_1707%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Jan Steen</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/81/Steen_Doctor_and_His_Patient.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>1660</t>
-  </si>
-  <si>
-    <t>La Fille malade</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+    <t>Table du petit-déjeuner avec tarte aux mûres</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/88/Rembrandt_Harmensz._van_Rijn_026.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>1636-1643</t>
+  </si>
+  <si>
+    <t>Danae</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/7f/W_Van_De_Velde%2C_Calm_-_Fishing_Boats_Under_Sail%2C_1655-60%2C_Wallace_Collection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Bateaux de pêche sous voile</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Van_Dyck_Charles_I_1635.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
@@ -736,13 +622,25 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg/1280px-Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/69/Analyasis_of_Las_Meninas.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg/1280px-Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Frans_Hals_%E2%80%93_The_Laughing_Cavalier.jpg/960px-Frans_Hals_%E2%80%93_The_Laughing_Cavalier.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cc/Georges_de_La_Tour_007.jpg/960px-Georges_de_La_Tour_007.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg/1280px-Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f8/Dou%2C_Gerard_-_Astronomer_by_Candlelight_-_late_1650.jpg/960px-Dou%2C_Gerard_-_Astronomer_by_Candlelight_-_late_1650.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1f/Hendrick_Avercamp_-_Winterlandschap_met_ijsvermaak.jpg/1280px-Hendrick_Avercamp_-_Winterlandschap_met_ijsvermaak.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
@@ -754,31 +652,28 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Goyen_1651_View_of_Dordrecht.jpg/1280px-Goyen_1651_View_of_Dordrecht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/Meindert_Hobbema_001.jpg/1280px-Meindert_Hobbema_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c5/Johannes_Vermeer_-_View_of_Delft_-_92_-_Mauritshuis.jpg/1280px-Johannes_Vermeer_-_View_of_Delft_-_92_-_Mauritshuis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/76/Judith_Leyster_The_Proposition.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg/1280px-Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Judith_et_sa_servante%2C_par_Orazio_Gentileschi.jpg/960px-Judith_et_sa_servante%2C_par_Orazio_Gentileschi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6e/Ceiling_of_Palazzo_Barberini.jpg/960px-Ceiling_of_Palazzo_Barberini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/26/Stilleven_met_vergulde_bokaal_Rijksmuseum_SK-A-4830.jpeg/1280px-Stilleven_met_vergulde_bokaal_Rijksmuseum_SK-A-4830.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg/1280px-Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Rembrandt_-_The_Anatomy_Lesson_of_Dr_Nicolaes_Tulp.jpg/1280px-Rembrandt_-_The_Anatomy_Lesson_of_Dr_Nicolaes_Tulp.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg/1280px-Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>Antoine van DYCK</t>
@@ -808,13 +703,34 @@
     <t>GUERCINO ou GUERCHIN</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/48/The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg/1280px-The_Calling_of_Saint_Matthew-Caravaggo_%281599-1600%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-  </si>
-  <si>
-    <t>Eglise Saint-Louis-des-Français, Rome</t>
-  </si>
-  <si>
-    <t>La Vocation de saint Matthieu</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/David_with_the_Head_of_Goliath-Caravaggio_%281610%29.jpg/960px-David_with_the_Head_of_Goliath-Caravaggio_%281610%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>David avec la tête de Goliath</t>
+  </si>
+  <si>
+    <t>Le Souper à Emmaüs</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c0/Supper_at_Emmaus-Caravaggio_%281601%29.jpg/1280px-Supper_at_Emmaus-Caravaggio_%281601%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/8a/Valentin_de_Boulogne%2C_Judgment_of_Solomon_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Valentin de Boulogne</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/Gian_Lorenzo_Bernini%2C_self-portrait%2C_c1623.jpg/960px-Gian_Lorenzo_Bernini%2C_self-portrait%2C_c1623.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Gian Lorenzo Bernini</t>
+  </si>
+  <si>
+    <t>Galerie Borghese, Rome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autoportrait </t>
   </si>
 </sst>
 </file>
@@ -867,7 +783,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -900,7 +816,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -910,9 +826,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1246,614 +1159,614 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>219</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>183</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>182</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>254</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>235</v>
+        <v>158</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>253</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="7" customFormat="1">
+      <c r="A8" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="C8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="E8" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>220</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1600</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>43</v>
+        <v>220</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1610</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1601</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="7" customFormat="1">
+      <c r="A12" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C12" s="4">
-        <v>1600</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>264</v>
+      <c r="D12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="4">
-        <v>1635</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="7" customFormat="1">
+      <c r="A14" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="7" customFormat="1">
+      <c r="A15" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>237</v>
+        <v>162</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>59</v>
+        <v>222</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1643</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C17" s="4">
-        <v>1643</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="7" customFormat="1">
+      <c r="A17" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="7" customFormat="1">
+      <c r="A18" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>258</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>239</v>
+        <v>165</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>199</v>
+        <v>70</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="13.5" customHeight="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>205</v>
+        <v>171</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1651</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>17</v>
+        <v>174</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>233</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>243</v>
+        <v>176</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C37" s="4">
-        <v>1651</v>
+        <v>113</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>209</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1861,469 +1774,471 @@
         <v>210</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" s="8" customFormat="1">
-      <c r="A41" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C41" s="7">
-        <v>1634</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>212</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C43" s="4">
-        <v>1663</v>
+        <v>125</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>219</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>156</v>
+        <v>7</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>159</v>
+        <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>222</v>
+        <v>8</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C56" s="4">
-        <v>1649</v>
+        <v>150</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>225</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>128</v>
+        <v>14</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>30</v>
+        <v>224</v>
+      </c>
+      <c r="C59" s="4">
+        <v>1655</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>13</v>
+        <v>232</v>
+      </c>
+      <c r="C60" s="4">
+        <v>1625</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>120</v>
+        <v>234</v>
+      </c>
+      <c r="C61" s="4">
+        <v>1623</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>17</v>
+        <v>235</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{B31B01AA-74C8-4C6A-9D2E-0738835BAD39}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{B67A90D2-FF44-475A-A10F-D246294B867F}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{0A6A3DED-DD12-4780-B3AE-753A687E8FBB}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{1B59958E-18C4-44A5-910B-4A37D44E0416}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{BF908DEB-302B-4A7D-9647-D1EFA4FA35C0}"/>
-    <hyperlink ref="A8" r:id="rId6" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
-    <hyperlink ref="A9" r:id="rId7" xr:uid="{443377B4-B04D-403D-A824-DB13768731AF}"/>
-    <hyperlink ref="A10" r:id="rId8" xr:uid="{96AEEB4F-086F-426E-B93A-2DA57DE54BFE}"/>
-    <hyperlink ref="A14" r:id="rId9" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
-    <hyperlink ref="A17" r:id="rId10" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
-    <hyperlink ref="A19" r:id="rId11" xr:uid="{05771483-93F6-4474-B4B2-32295BDD81BC}"/>
-    <hyperlink ref="A20" r:id="rId12" xr:uid="{55E726A8-6C5A-40E3-B1C5-B4EC6C735238}"/>
-    <hyperlink ref="A21" r:id="rId13" xr:uid="{2AB88B44-F231-4B4B-A7BD-4C589B3E43E3}"/>
-    <hyperlink ref="A15" r:id="rId14" xr:uid="{410386BC-CF6D-4493-8184-0403996A2394}"/>
-    <hyperlink ref="A23" r:id="rId15" xr:uid="{08DD652B-0E47-4AEF-AE3B-843EED3B5D37}"/>
-    <hyperlink ref="A24" r:id="rId16" xr:uid="{E1C8A8CF-4AE8-4C17-BE5B-9FAE82B663F7}"/>
-    <hyperlink ref="A26" r:id="rId17" xr:uid="{636B89F5-0780-4E07-8ECA-A1510576ABCD}"/>
-    <hyperlink ref="A27" r:id="rId18" xr:uid="{74A7EC9A-D21C-4ECC-949D-FCC02E532D40}"/>
-    <hyperlink ref="A28" r:id="rId19" xr:uid="{9D3E1C27-FE83-4482-8C5F-CC33FCC1E2C6}"/>
-    <hyperlink ref="A29" r:id="rId20" xr:uid="{7E575697-1670-41B2-BC75-9872FD034F04}"/>
-    <hyperlink ref="A31" r:id="rId21" xr:uid="{E9D4827D-694A-41D2-9587-D78CF34633D6}"/>
-    <hyperlink ref="A32" r:id="rId22" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
-    <hyperlink ref="A34" r:id="rId23" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
-    <hyperlink ref="A35" r:id="rId24" xr:uid="{F55798B2-2CE8-4A25-815E-90D86322A818}"/>
-    <hyperlink ref="A38" r:id="rId25" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
-    <hyperlink ref="A39" r:id="rId26" xr:uid="{3BE0486C-7F43-481A-86BD-951F21E28A4C}"/>
-    <hyperlink ref="A42" r:id="rId27" xr:uid="{C2924DD1-C68C-444A-A0E3-59C8E373AD89}"/>
-    <hyperlink ref="A43" r:id="rId28" xr:uid="{75B759AD-4F67-448E-B557-AEA72EFC75A5}"/>
-    <hyperlink ref="A44" r:id="rId29" xr:uid="{CD9775EB-2654-4C75-971C-D0D4D92F6FFA}"/>
-    <hyperlink ref="A46" r:id="rId30" xr:uid="{5EB8FE73-1B38-4EE8-9F5D-408471533360}"/>
-    <hyperlink ref="A51" r:id="rId31" xr:uid="{FA4FAF58-BD57-4E39-9226-854692AFB81E}"/>
-    <hyperlink ref="A52" r:id="rId32" xr:uid="{148877A9-A1F7-456C-A81C-37672CB63775}"/>
-    <hyperlink ref="A53" r:id="rId33" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
-    <hyperlink ref="A55" r:id="rId34" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
-    <hyperlink ref="A56" r:id="rId35" xr:uid="{B20C8042-5197-411A-8C08-02B3412DF1B5}"/>
-    <hyperlink ref="A57" r:id="rId36" xr:uid="{2C4AA8F5-D564-4836-B8DB-CC33D50B9F4C}"/>
-    <hyperlink ref="A58" r:id="rId37" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
-    <hyperlink ref="A36" r:id="rId38" xr:uid="{4E0A47A0-C017-478F-882E-CB36E0739B68}"/>
-    <hyperlink ref="A41" r:id="rId39" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg/1280px-Arbre_de_bambou_et_prune_dans_la_neige_par_Kan%C5%8D_Tanny%C5%AB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5AF78C13-26E9-461E-B73A-B7874AC748C6}"/>
-    <hyperlink ref="A7" r:id="rId40" xr:uid="{8F4B7051-A843-4632-824C-A44F2EFF1A24}"/>
-    <hyperlink ref="A11" r:id="rId41" xr:uid="{AB2FF381-1824-400A-9BCD-9866E6CB0543}"/>
-    <hyperlink ref="A13" r:id="rId42" xr:uid="{DCC4F749-42F9-4EA6-B692-38BDBFED8233}"/>
-    <hyperlink ref="A16" r:id="rId43" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D4203C8E-14B3-4039-BB62-7E3865A15809}"/>
-    <hyperlink ref="A18" r:id="rId44" xr:uid="{4E85BF3A-C7F1-4E5B-9573-8D70D234C5FE}"/>
-    <hyperlink ref="A22" r:id="rId45" xr:uid="{5CD46D31-5953-4A01-A434-5588D8535138}"/>
-    <hyperlink ref="A25" r:id="rId46" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg/1280px-Le_Tricheur_%C3%A0_l%27as_de_carreau_-_Georges_de_La_Tour_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1972_8.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CEC1CD09-7664-45E7-A13A-1C89874F9D17}"/>
-    <hyperlink ref="A30" r:id="rId47" xr:uid="{0F121F29-C0EE-4A69-9EFA-A138C1AB816A}"/>
-    <hyperlink ref="A33" r:id="rId48" xr:uid="{462E3B14-36A0-4360-9820-4A3EBD2EFC5E}"/>
-    <hyperlink ref="A37" r:id="rId49" xr:uid="{D9F18DF3-6619-40EF-97D9-920D7EDAF9C0}"/>
-    <hyperlink ref="A40" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5c/Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg/1920px-Judith_Leyster%2C_Self-Portrait%2C_c._1630%2C_NGA_37003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96CB3FBB-D488-4EA8-947C-196A5F59B5CC}"/>
-    <hyperlink ref="A45" r:id="rId51" xr:uid="{2DED679E-C744-4A9B-BE0E-3AC4E0186B76}"/>
-    <hyperlink ref="A47" r:id="rId52" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E3A7419A-96A2-4726-8D79-92D233EEF839}"/>
-    <hyperlink ref="A48" r:id="rId53" xr:uid="{3DA6F16C-EF9E-4846-A7D5-E3E407DD7B4C}"/>
-    <hyperlink ref="A49" r:id="rId54" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg/960px-Barbara_Villiers%2C_Duchess_of_Cleveland%2C_1662_by_Lely.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{35574EF1-90A2-4482-A075-ABF3F82885AB}"/>
-    <hyperlink ref="A50" r:id="rId55" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{6BB625E2-11FD-4585-B272-667B24656B6E}"/>
-    <hyperlink ref="A54" r:id="rId56" xr:uid="{83398DF1-6CCA-4D96-A783-0FE96B2E9F31}"/>
-    <hyperlink ref="A59" r:id="rId57" xr:uid="{83B8C51F-09BE-47B7-B07C-3A8576A86413}"/>
-    <hyperlink ref="A60" r:id="rId58" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png/1280px-Willem_Kalf%2C_Still_Life_with_Drinking-Horn%2C_c._1653%2C_oil_on_canvas%2C_National_Gallery.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{66426EEF-8035-4F74-A518-75CD002F4D21}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{1A7C0D1A-8696-4142-A459-3A501936D346}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{A9F291AE-CE9E-473E-9CE6-C39E797E2926}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{7E0DEBF1-9967-4A4C-8099-60B9DEB5D6A8}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{546CD3A0-4594-432F-814F-E62DAAAC6D34}"/>
+    <hyperlink ref="A7" r:id="rId5" xr:uid="{B1D18D5B-F033-4CBC-8258-80D80B3D6B1A}"/>
+    <hyperlink ref="A9" r:id="rId6" xr:uid="{72C00A77-DE47-4350-ABDF-53A01568DB8C}"/>
+    <hyperlink ref="A13" r:id="rId7" xr:uid="{26C60298-1859-49FC-B93F-6E2DBE064D95}"/>
+    <hyperlink ref="A16" r:id="rId8" xr:uid="{1A7A1C2D-9BDA-4D6C-AB0D-298B63D4B420}"/>
+    <hyperlink ref="A19" r:id="rId9" xr:uid="{AEA087D1-239A-45A8-B8E2-097CE49E0FA2}"/>
+    <hyperlink ref="A20" r:id="rId10" xr:uid="{418161AA-1108-438A-A40F-FEEBCEEA59A7}"/>
+    <hyperlink ref="A22" r:id="rId11" xr:uid="{08DD652B-0E47-4AEF-AE3B-843EED3B5D37}"/>
+    <hyperlink ref="A23" r:id="rId12" xr:uid="{08D60088-499F-44EC-99C8-8B92DAABE16C}"/>
+    <hyperlink ref="A27" r:id="rId13" xr:uid="{4D57808A-EF9C-4AA9-BA44-1512D9D61C6C}"/>
+    <hyperlink ref="A28" r:id="rId14" xr:uid="{C494AD1B-E0CA-4F10-84B5-455B27655F83}"/>
+    <hyperlink ref="A29" r:id="rId15" xr:uid="{7E575697-1670-41B2-BC75-9872FD034F04}"/>
+    <hyperlink ref="A31" r:id="rId16" xr:uid="{C423AE40-5C52-44E9-846A-DCBE38942E39}"/>
+    <hyperlink ref="A33" r:id="rId17" xr:uid="{854D64A5-0416-4CA8-BA54-6104DE34FE41}"/>
+    <hyperlink ref="A34" r:id="rId18" xr:uid="{F95E6437-8FC2-4E97-BB2A-3A078AEE787C}"/>
+    <hyperlink ref="A36" r:id="rId19" xr:uid="{9F33292D-E11B-47E3-A758-5369AF1AFBB7}"/>
+    <hyperlink ref="A37" r:id="rId20" xr:uid="{FDEB65E8-E3C9-4173-A3A5-699B556167FB}"/>
+    <hyperlink ref="A39" r:id="rId21" xr:uid="{3BE0486C-7F43-481A-86BD-951F21E28A4C}"/>
+    <hyperlink ref="A41" r:id="rId22" xr:uid="{C2924DD1-C68C-444A-A0E3-59C8E373AD89}"/>
+    <hyperlink ref="A42" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a5/%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg/1920px-%22La_forge%22%2C_Louis_Le_Nain%2C_vers_1640-1642._Mus%C3%A9e_du_Louvre._%2835366251024%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F15F6E3C-73ED-4C57-8C55-43394AFB2AB2}"/>
+    <hyperlink ref="A43" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/d2/Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg/1280px-Firenze_Palazzo_Medici_Riccardi_Interno_Galleria_Soffitto_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{444BA55E-6438-4CFB-9303-997E4FF662A1}"/>
+    <hyperlink ref="A46" r:id="rId25" xr:uid="{7D7AB562-1695-44D3-9302-EB9B70CAA7E3}"/>
+    <hyperlink ref="A49" r:id="rId26" xr:uid="{DEDAFC51-2102-44FE-845E-028590F63B54}"/>
+    <hyperlink ref="A50" r:id="rId27" xr:uid="{DF73CDA4-CEF8-4638-BBC0-C361102BEE04}"/>
+    <hyperlink ref="A51" r:id="rId28" xr:uid="{90544544-956B-488D-9781-06680F0DA998}"/>
+    <hyperlink ref="A52" r:id="rId29" xr:uid="{5F76217F-4F6B-4D31-BC66-876467E7E67C}"/>
+    <hyperlink ref="A55" r:id="rId30" xr:uid="{15CF0BF0-994A-4A35-9671-66A095B35CD8}"/>
+    <hyperlink ref="A56" r:id="rId31" xr:uid="{2C4AA8F5-D564-4836-B8DB-CC33D50B9F4C}"/>
+    <hyperlink ref="A57" r:id="rId32" xr:uid="{30960AA4-BF0A-418D-B786-3593B23BD377}"/>
+    <hyperlink ref="A54" r:id="rId33" xr:uid="{70262521-5303-465D-8B9D-47AE4E0F2D2A}"/>
+    <hyperlink ref="A59" r:id="rId34" xr:uid="{A14CE758-CBAB-4381-8BBB-15948337FAD9}"/>
+    <hyperlink ref="A3" r:id="rId35" xr:uid="{945251CC-E6AD-4661-9571-02B7C81C2515}"/>
+    <hyperlink ref="A8" r:id="rId36" xr:uid="{AE09BF63-612F-4029-93B7-0FFC6478EC80}"/>
+    <hyperlink ref="A12" r:id="rId37" xr:uid="{A4E016D8-8E8B-4277-888D-5A265E16A6CA}"/>
+    <hyperlink ref="A14" r:id="rId38" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{596E240E-7D53-4A32-9D33-569DA93A4937}"/>
+    <hyperlink ref="A15" r:id="rId39" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg/1280px-Claude_Lorrain_-_Seaport_with_the_Embarkation_of_the_Queen_of_Sheba_-_WGA05002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EBCA20AC-1D38-4222-AB4E-BF68B3C90D3C}"/>
+    <hyperlink ref="A17" r:id="rId40" xr:uid="{EF15C00B-27CF-44B6-8670-F310C1BB94A2}"/>
+    <hyperlink ref="A18" r:id="rId41" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg/1280px-Vel%C3%A1zquez_-_de_Breda_o_Las_Lanzas_%28Museo_del_Prado%2C_1634-35%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57BDA7C2-2097-4285-8501-5706AF6C54CB}"/>
+    <hyperlink ref="A21" r:id="rId42" xr:uid="{59CEEA06-FA81-4ACE-8191-838FE9BA1BF7}"/>
+    <hyperlink ref="A24" r:id="rId43" xr:uid="{4B07A603-5273-44D0-B268-760021F85005}"/>
+    <hyperlink ref="A25" r:id="rId44" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg/1280px-Georges_de_La_Tour_-_Newlyborn_infant_-_Mus%C3%A9e_des_Beaux-Arts_de_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{10E006E8-2443-4060-9149-E3123D594459}"/>
+    <hyperlink ref="A26" r:id="rId45" xr:uid="{302BFBD5-CCBC-44D9-B9D7-53DC45FF1E20}"/>
+    <hyperlink ref="A30" r:id="rId46" xr:uid="{3028B9B6-1977-4385-A1C6-3FAEC26A346D}"/>
+    <hyperlink ref="A32" r:id="rId47" xr:uid="{975264BA-C514-413E-99EA-DD14D58AB288}"/>
+    <hyperlink ref="A35" r:id="rId48" xr:uid="{86A34B4C-C537-4D76-A3EA-321DD50D8CB1}"/>
+    <hyperlink ref="A38" r:id="rId49" xr:uid="{072FFDC6-2747-4BB4-BC37-0C70594E6F4D}"/>
+    <hyperlink ref="A40" r:id="rId50" xr:uid="{C594B535-2481-40E5-9C7D-7ED4B45F7645}"/>
+    <hyperlink ref="A44" r:id="rId51" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg/1280px-Meindert_Hobbema_-_Een_watermolen_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9552E73C-3D36-4755-AB33-97007CDF5358}"/>
+    <hyperlink ref="A45" r:id="rId52" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/0d/Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg/1280px-Les_Bergers_d%27Arcadie_-_Nicolas_Poussin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_7300_%3B_MR_2339.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06C35A77-A512-486F-96AF-3B12DCA46F8F}"/>
+    <hyperlink ref="A47" r:id="rId53" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a1/Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg/1280px-Peter_Paul_Rubens_-_Descent_from_the_Cross_-_WGA20212.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{0DEC1873-EA8A-4837-A600-314F517B37B3}"/>
+    <hyperlink ref="A48" r:id="rId54" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg/1280px-Peter_Paul_Rubens_-_Raising_of_the_Cross_%28Cathedral_of_Antwerp%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{975F1E1C-791A-4C4E-BECF-5701732F6721}"/>
+    <hyperlink ref="A53" r:id="rId55" xr:uid="{1C87A638-94E8-40B9-A0F1-C41FE40A0E7B}"/>
+    <hyperlink ref="A58" r:id="rId56" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg/1280px-Willem_Clasz._Heda_-_Breakfast_Table_with_Blackberry_Pie_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0E287FD2-4B38-4DE9-96FA-D2FE3EE0C624}"/>
+    <hyperlink ref="A10" r:id="rId57" xr:uid="{2E22A58C-17B1-4A26-A346-B2B74239110E}"/>
+    <hyperlink ref="A11" r:id="rId58" xr:uid="{313F2464-066F-4F8B-B7A6-8668093EF425}"/>
+    <hyperlink ref="A60" r:id="rId59" xr:uid="{7D96CBCA-D1BD-4217-84EC-B9D037E8C421}"/>
+    <hyperlink ref="A61" r:id="rId60" xr:uid="{8FF641D2-70B4-4EAF-BD83-EC08F50176C4}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-17e-niveau2.xlsx
+++ b/quizzes/peinture-17e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{412EDAC4-2567-41C6-BDCF-9DA8B62173A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3909B0DC-F8D1-4E8D-AB3D-3A185B800EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="344">
   <si>
     <t>image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/1/16/Annibale_Carracci_-_Domine_quo_vadis%3F_-_WGA04444.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>77,4 × 56,3 cm</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Van_Dyck_Charles_I_1635.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -91,6 +97,9 @@
     <t>266 × 207 cm</t>
   </si>
   <si>
+    <t>flamande (Belgique)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/98/Anthonis_van_Dyck_-_Equestrian_Portrait_of_Charles_I_-_National_Gallery%2C_London.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -160,6 +169,9 @@
     <t>146 × 104 cm</t>
   </si>
   <si>
+    <t>espagnole</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/87/Bernardo_Strozzi_-_The_Cook_-_WGA21913.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
@@ -241,6 +253,9 @@
     <t>33,5 × 22,8 cm</t>
   </si>
   <si>
+    <t>hollandaise (Pays-Bas)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Charles_Le_Brun_-_Pierre_S%C3%A9guier%2C_chancelier_de_France_%281655-1661%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -257,6 +272,9 @@
   </si>
   <si>
     <t>295 × 351 cm</t>
+  </si>
+  <si>
+    <t>française</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg/1280px-Le_d%C3%A9barquement_de_Cl%C3%A9op%C3%A2tre_%C3%A0_Tarse_-_1642-1643_-_Claude_Gell%C3%A9e_dit_le_Lorrain_-_Louvre_-_INV_4716_%3B_MR_1738.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
@@ -1446,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="77.85546875" customWidth="1"/>
@@ -1458,7 +1476,7 @@
     <col min="7" max="8" width="29.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" ht="24.95" customHeight="1">
+    <row r="1" spans="1:9" s="7" customFormat="1" ht="24.95" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1483,1547 +1501,1730 @@
       <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="C6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="G6" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="3" customFormat="1">
+        <v>48</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="3" customFormat="1">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>56</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C9" s="2">
         <v>1600</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="C10" s="5">
         <v>1610</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>66</v>
+      </c>
+      <c r="I10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2">
         <v>1601</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="3" customFormat="1">
+        <v>69</v>
+      </c>
+      <c r="I11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="3" customFormat="1">
       <c r="A12" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>76</v>
+      </c>
+      <c r="I12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="3" customFormat="1">
+        <v>83</v>
+      </c>
+      <c r="I13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="3" customFormat="1">
       <c r="A14" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="3" customFormat="1">
+    <row r="15" spans="1:9" s="3" customFormat="1">
       <c r="A15" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>94</v>
+      </c>
+      <c r="I15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C16" s="5">
         <v>1643</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" s="3" customFormat="1">
+        <v>99</v>
+      </c>
+      <c r="I16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="3" customFormat="1">
       <c r="A17" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F17" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="3" customFormat="1">
+      <c r="A18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="3" customFormat="1">
-      <c r="A18" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>141</v>
+      </c>
+      <c r="I23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>146</v>
+      </c>
+      <c r="I24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>152</v>
+      </c>
+      <c r="I25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>99</v>
+      </c>
+      <c r="I26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>164</v>
+      </c>
+      <c r="I27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>172</v>
+      </c>
+      <c r="I28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="E29" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>179</v>
+      </c>
+      <c r="I29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>99</v>
+      </c>
+      <c r="I30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>99</v>
+      </c>
+      <c r="I31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>195</v>
+      </c>
+      <c r="I32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>201</v>
+      </c>
+      <c r="I33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>207</v>
+      </c>
+      <c r="I34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C35" s="5">
         <v>1651</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>99</v>
+      </c>
+      <c r="I35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>216</v>
+      </c>
+      <c r="I36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F37" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="I37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="C38" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>225</v>
+      </c>
+      <c r="I38" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>231</v>
+      </c>
+      <c r="I39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="I40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>242</v>
+      </c>
+      <c r="I41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>246</v>
+      </c>
+      <c r="I42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>172</v>
+      </c>
+      <c r="I43" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>99</v>
+      </c>
+      <c r="I44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>262</v>
+      </c>
+      <c r="I45" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>265</v>
+      </c>
+      <c r="I46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>272</v>
+      </c>
+      <c r="I47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="C48" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>277</v>
+      </c>
+      <c r="I48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>283</v>
+      </c>
+      <c r="I49" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>99</v>
+      </c>
+      <c r="I50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>294</v>
+      </c>
+      <c r="I51" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>299</v>
+      </c>
+      <c r="I52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="I53" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="C54" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>307</v>
+      </c>
+      <c r="I54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>99</v>
+      </c>
+      <c r="I55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>318</v>
+      </c>
+      <c r="I56" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>323</v>
+      </c>
+      <c r="I57" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>328</v>
+      </c>
+      <c r="I58" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C59" s="5">
         <v>1655</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>99</v>
+      </c>
+      <c r="I59" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C60" s="5">
         <v>1625</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>337</v>
+      </c>
+      <c r="I60" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C61" s="5">
         <v>1623</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
+      </c>
+      <c r="I61" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
